--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,7 +557,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -571,7 +571,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -585,7 +585,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -597,13 +597,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -611,11 +611,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>45900</v>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>43239</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -624,10 +626,10 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -636,10 +638,10 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -648,10 +650,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -660,10 +662,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -672,10 +674,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -684,10 +686,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -696,10 +698,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -708,10 +710,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -720,10 +722,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -732,10 +734,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -744,10 +746,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -756,10 +758,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -768,10 +770,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -780,10 +782,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -792,10 +794,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -804,10 +806,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -816,10 +818,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -828,10 +830,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -840,10 +842,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -852,10 +854,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -864,10 +866,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -876,10 +878,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -888,7 +890,7 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>35700</v>
@@ -900,10 +902,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -912,10 +914,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -924,10 +926,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -936,10 +938,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -948,10 +950,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -960,10 +962,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -972,10 +974,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -984,10 +986,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -996,10 +998,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1008,10 +1010,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1020,10 +1022,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1032,10 +1034,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1044,10 +1046,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1056,10 +1058,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1068,10 +1070,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1080,10 +1082,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1092,10 +1094,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1104,10 +1106,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1116,10 +1118,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1128,10 +1130,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1140,10 +1142,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1152,10 +1154,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1164,10 +1166,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1175,7 +1177,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n"/>
+      <c r="A62" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
         <v/>
@@ -1260,6 +1267,13 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
+      <c r="C74">
+        <f>(B74/B86-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,7 +529,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,7 +571,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -585,7 +585,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -599,7 +599,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -611,13 +611,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -625,11 +625,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>45900</v>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>43239</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -638,10 +640,10 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -650,10 +652,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -662,10 +664,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -674,10 +676,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -686,10 +688,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -698,10 +700,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -710,10 +712,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -722,10 +724,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -734,10 +736,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -746,10 +748,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -758,10 +760,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -770,10 +772,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -782,10 +784,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -794,10 +796,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -806,10 +808,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -818,10 +820,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -830,10 +832,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -842,10 +844,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -854,10 +856,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -866,10 +868,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -878,10 +880,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -890,10 +892,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -902,7 +904,7 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>35700</v>
@@ -914,10 +916,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -926,10 +928,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -938,10 +940,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -950,10 +952,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -962,10 +964,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -974,10 +976,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -986,10 +988,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -998,10 +1000,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1010,10 +1012,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1022,10 +1024,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1034,10 +1036,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1046,10 +1048,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1058,10 +1060,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1070,10 +1072,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1082,10 +1084,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1094,10 +1096,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1106,10 +1108,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1118,10 +1120,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1130,10 +1132,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1142,10 +1144,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1154,10 +1156,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1166,10 +1168,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1178,10 +1180,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1189,7 +1191,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n"/>
+      <c r="A63" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
         <v/>
@@ -1274,6 +1281,13 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
+      <c r="C75">
+        <f>(B75/B87-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,7 +459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,7 +543,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,7 +585,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -599,7 +599,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -625,13 +625,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -639,11 +639,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>45900</v>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>43239</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -652,10 +654,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -664,10 +666,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -676,10 +678,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -688,10 +690,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -700,10 +702,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -712,10 +714,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -724,10 +726,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -736,10 +738,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -748,10 +750,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -760,10 +762,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -772,10 +774,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -784,10 +786,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -796,10 +798,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -808,10 +810,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -820,10 +822,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -832,10 +834,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -844,10 +846,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -856,10 +858,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -868,10 +870,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -880,10 +882,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -892,10 +894,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -904,10 +906,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -916,7 +918,7 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>35700</v>
@@ -928,10 +930,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -940,10 +942,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -952,10 +954,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -964,10 +966,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -976,10 +978,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -988,10 +990,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1000,10 +1002,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1012,10 +1014,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1024,10 +1026,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1036,10 +1038,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1048,10 +1050,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1060,10 +1062,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1072,10 +1074,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1084,10 +1086,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1096,10 +1098,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1108,10 +1110,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1120,10 +1122,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1132,10 +1134,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1144,10 +1146,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1156,10 +1158,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1168,10 +1170,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1180,10 +1182,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1192,10 +1194,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1203,7 +1205,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
+      <c r="A64" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
         <v/>
@@ -1288,6 +1295,13 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
+      <c r="C76">
+        <f>(B76/B88-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,7 +557,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,7 +599,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -627,7 +627,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -639,13 +639,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C17">
         <f>(B17/B29-1)*100</f>
@@ -653,11 +653,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>45900</v>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>43239</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -666,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -678,10 +680,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -690,10 +692,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -702,10 +704,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -714,10 +716,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -726,10 +728,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -738,10 +740,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -750,10 +752,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -762,10 +764,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -774,10 +776,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -786,10 +788,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -798,10 +800,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -810,10 +812,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -822,10 +824,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -834,10 +836,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -846,10 +848,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -858,10 +860,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -870,10 +872,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -882,10 +884,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -894,10 +896,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -906,10 +908,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -918,10 +920,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -930,7 +932,7 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>35700</v>
@@ -942,10 +944,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -954,10 +956,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -966,10 +968,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -978,10 +980,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -990,10 +992,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1002,10 +1004,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1014,10 +1016,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1026,10 +1028,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1038,10 +1040,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1050,10 +1052,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1062,10 +1064,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1074,10 +1076,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1086,10 +1088,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1098,10 +1100,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1110,10 +1112,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1122,10 +1124,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1134,10 +1136,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1146,10 +1148,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1158,10 +1160,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1170,10 +1172,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1182,10 +1184,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1194,10 +1196,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1206,10 +1208,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1217,7 +1219,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n"/>
+      <c r="A65" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
         <v/>
@@ -1302,6 +1309,13 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
+      <c r="C77">
+        <f>(B77/B89-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -459,11 +459,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C4">
         <f>(B4/B16-1)*100</f>
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,7 +487,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,7 +571,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -627,7 +627,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -641,7 +641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -653,13 +653,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C18">
         <f>(B18/B30-1)*100</f>
@@ -667,11 +667,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>45900</v>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>43239</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -680,10 +682,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -692,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -704,10 +706,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -716,10 +718,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -728,10 +730,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -740,10 +742,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -752,10 +754,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -764,10 +766,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -776,10 +778,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -788,10 +790,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -800,10 +802,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -812,10 +814,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -824,10 +826,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -836,10 +838,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -848,10 +850,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -860,10 +862,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -872,10 +874,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -884,10 +886,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -896,10 +898,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -908,10 +910,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -920,10 +922,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -932,10 +934,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -944,7 +946,7 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>35700</v>
@@ -956,10 +958,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -968,10 +970,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -980,10 +982,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -992,10 +994,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1004,10 +1006,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1016,10 +1018,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1028,10 +1030,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1040,10 +1042,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1052,10 +1054,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1064,10 +1066,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1076,10 +1078,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1088,10 +1090,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1100,10 +1102,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1112,10 +1114,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1124,10 +1126,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1136,10 +1138,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1148,10 +1150,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1160,10 +1162,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1172,10 +1174,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1184,10 +1186,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1196,10 +1198,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1208,10 +1210,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1220,10 +1222,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1231,7 +1233,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n"/>
+      <c r="A66" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
         <v/>
@@ -1316,6 +1323,13 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
+      <c r="C78">
+        <f>(B78/B90-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.3</v>
+        <v>38014</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -459,7 +459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -473,11 +473,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C5">
         <f>(B5/B17-1)*100</f>
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,7 +501,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -515,11 +515,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C8">
         <f>(B8/B20-1)*100</f>
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,7 +585,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -599,11 +599,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C14">
         <f>(B14/B26-1)*100</f>
@@ -613,11 +613,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -627,7 +627,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -641,7 +641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -655,7 +655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -667,13 +667,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C19">
         <f>(B19/B31-1)*100</f>
@@ -681,11 +681,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>45900</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>43239</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -694,10 +696,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -706,10 +708,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -718,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -730,10 +732,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -742,10 +744,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -754,10 +756,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -766,10 +768,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -778,10 +780,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -790,10 +792,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -802,10 +804,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -814,10 +816,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -826,10 +828,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -838,10 +840,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -850,10 +852,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -862,10 +864,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -874,10 +876,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -886,10 +888,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -898,10 +900,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -910,10 +912,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -922,10 +924,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -934,10 +936,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -946,10 +948,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -958,7 +960,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>35700</v>
@@ -970,10 +972,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C44">
         <f>(B44/B56-1)*100</f>
@@ -982,10 +984,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -994,10 +996,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1006,10 +1008,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1018,10 +1020,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1030,10 +1032,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1042,10 +1044,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1054,10 +1056,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1066,10 +1068,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1078,10 +1080,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1090,10 +1092,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1102,10 +1104,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1114,10 +1116,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1126,10 +1128,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1138,10 +1140,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1150,10 +1152,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1162,10 +1164,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1174,10 +1176,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1186,10 +1188,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1198,10 +1200,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1210,10 +1212,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1222,10 +1224,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1234,10 +1236,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1245,7 +1247,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n"/>
+      <c r="A67" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
         <v/>
@@ -1330,6 +1337,13 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
+      <c r="C79">
+        <f>(B79/B91-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/home-sales.xlsx
+++ b/data/home-sales.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" customWidth="1" style="2" min="1" max="1"/>
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38014</v>
+        <v>69.3</v>
       </c>
       <c r="C2">
         <f>(B2/B14-1)*100</f>
@@ -445,11 +445,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.3</v>
+        <v>38014</v>
       </c>
       <c r="C3">
         <f>(B3/B15-1)*100</f>
@@ -459,7 +459,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -487,11 +487,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C6">
         <f>(B6/B18-1)*100</f>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C7">
         <f>(B7/B19-1)*100</f>
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -529,11 +529,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.7</v>
+        <v>69.3</v>
       </c>
       <c r="C9">
         <f>(B9/B21-1)*100</f>
@@ -543,11 +543,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.3</v>
+        <v>66.7</v>
       </c>
       <c r="C10">
         <f>(B10/B22-1)*100</f>
@@ -557,11 +557,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39938</v>
+        <v>69.3</v>
       </c>
       <c r="C11">
         <f>(B11/B23-1)*100</f>
@@ -571,11 +571,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40714</v>
+        <v>39938</v>
       </c>
       <c r="C12">
         <f>(B12/B24-1)*100</f>
@@ -585,11 +585,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.3</v>
+        <v>40714</v>
       </c>
       <c r="C13">
         <f>(B13/B25-1)*100</f>
@@ -599,7 +599,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -613,11 +613,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37626</v>
+        <v>69.3</v>
       </c>
       <c r="C15">
         <f>(B15/B27-1)*100</f>
@@ -627,11 +627,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66.8</v>
+        <v>37626</v>
       </c>
       <c r="C16">
         <f>(B16/B28-1)*100</f>
@@ -641,7 +641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -655,7 +655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -669,7 +669,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -681,13 +681,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43239</v>
+        <v>66.8</v>
       </c>
       <c r="C20">
         <f>(B20/B32-1)*100</f>
@@ -695,11 +695,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>45900</v>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>43239</v>
       </c>
       <c r="C21">
         <f>(B21/B33-1)*100</f>
@@ -708,10 +710,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>44200</v>
+        <v>45900</v>
       </c>
       <c r="C22">
         <f>(B22/B34-1)*100</f>
@@ -720,10 +722,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="C23">
         <f>(B23/B35-1)*100</f>
@@ -732,10 +734,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>40400</v>
+        <v>41200</v>
       </c>
       <c r="C24">
         <f>(B24/B36-1)*100</f>
@@ -744,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>39600</v>
+        <v>40400</v>
       </c>
       <c r="C25">
         <f>(B25/B37-1)*100</f>
@@ -756,10 +758,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>39800</v>
+        <v>45474</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>39600</v>
       </c>
       <c r="C26">
         <f>(B26/B38-1)*100</f>
@@ -768,10 +770,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>38300</v>
+        <v>39800</v>
       </c>
       <c r="C27">
         <f>(B27/B39-1)*100</f>
@@ -780,10 +782,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>38400</v>
+        <v>38300</v>
       </c>
       <c r="C28">
         <f>(B28/B40-1)*100</f>
@@ -792,10 +794,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>39700</v>
+        <v>38400</v>
       </c>
       <c r="C29">
         <f>(B29/B41-1)*100</f>
@@ -804,10 +806,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>39400</v>
+        <v>39700</v>
       </c>
       <c r="C30">
         <f>(B30/B42-1)*100</f>
@@ -816,10 +818,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>40300</v>
+        <v>39400</v>
       </c>
       <c r="C31">
         <f>(B31/B43-1)*100</f>
@@ -828,10 +830,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>38600</v>
+        <v>40300</v>
       </c>
       <c r="C32">
         <f>(B32/B44-1)*100</f>
@@ -840,10 +842,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>35200</v>
+        <v>38600</v>
       </c>
       <c r="C33">
         <f>(B33/B45-1)*100</f>
@@ -852,10 +854,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>35400</v>
+        <v>35200</v>
       </c>
       <c r="C34">
         <f>(B34/B46-1)*100</f>
@@ -864,10 +866,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>38600</v>
+        <v>35400</v>
       </c>
       <c r="C35">
         <f>(B35/B47-1)*100</f>
@@ -876,10 +878,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>39800</v>
+        <v>38600</v>
       </c>
       <c r="C36">
         <f>(B36/B48-1)*100</f>
@@ -888,10 +890,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>41300</v>
+        <v>39800</v>
       </c>
       <c r="C37">
         <f>(B37/B49-1)*100</f>
@@ -900,10 +902,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>41600</v>
+        <v>41300</v>
       </c>
       <c r="C38">
         <f>(B38/B50-1)*100</f>
@@ -912,10 +914,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>41700</v>
+        <v>41600</v>
       </c>
       <c r="C39">
         <f>(B39/B51-1)*100</f>
@@ -924,10 +926,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>39600</v>
+        <v>41700</v>
       </c>
       <c r="C40">
         <f>(B40/B52-1)*100</f>
@@ -936,10 +938,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>35700</v>
+        <v>39600</v>
       </c>
       <c r="C41">
         <f>(B41/B53-1)*100</f>
@@ -948,10 +950,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>35000</v>
+        <v>35700</v>
       </c>
       <c r="C42">
         <f>(B42/B54-1)*100</f>
@@ -960,10 +962,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>35700</v>
+        <v>44958</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>35000</v>
       </c>
       <c r="C43">
         <f>(B43/B55-1)*100</f>
@@ -972,7 +974,7 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>35700</v>
@@ -984,10 +986,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>35600</v>
+        <v>35700</v>
       </c>
       <c r="C45">
         <f>(B45/B57-1)*100</f>
@@ -996,10 +998,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>36400</v>
+        <v>35600</v>
       </c>
       <c r="C46">
         <f>(B46/B58-1)*100</f>
@@ -1008,10 +1010,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>36200</v>
+        <v>36400</v>
       </c>
       <c r="C47">
         <f>(B47/B59-1)*100</f>
@@ -1020,10 +1022,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>37300</v>
+        <v>36200</v>
       </c>
       <c r="C48">
         <f>(B48/B60-1)*100</f>
@@ -1032,10 +1034,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="C49">
         <f>(B49/B61-1)*100</f>
@@ -1044,10 +1046,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>39200</v>
+        <v>37600</v>
       </c>
       <c r="C50">
         <f>(B50/B62-1)*100</f>
@@ -1056,10 +1058,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>41900</v>
+        <v>39200</v>
       </c>
       <c r="C51">
         <f>(B51/B63-1)*100</f>
@@ -1068,10 +1070,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46600</v>
+        <v>41900</v>
       </c>
       <c r="C52">
         <f>(B52/B64-1)*100</f>
@@ -1080,10 +1082,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>53700</v>
+        <v>46600</v>
       </c>
       <c r="C53">
         <f>(B53/B65-1)*100</f>
@@ -1092,10 +1094,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>58200</v>
+        <v>53700</v>
       </c>
       <c r="C54">
         <f>(B54/B66-1)*100</f>
@@ -1104,10 +1106,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>57100</v>
+        <v>58200</v>
       </c>
       <c r="C55">
         <f>(B55/B67-1)*100</f>
@@ -1116,10 +1118,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>56700</v>
+        <v>57100</v>
       </c>
       <c r="C56">
         <f>(B56/B68-1)*100</f>
@@ -1128,10 +1130,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>58400</v>
+        <v>56700</v>
       </c>
       <c r="C57">
         <f>(B57/B69-1)*100</f>
@@ -1140,10 +1142,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>57400</v>
+        <v>58400</v>
       </c>
       <c r="C58">
         <f>(B58/B70-1)*100</f>
@@ -1152,10 +1154,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>53700</v>
+        <v>57400</v>
       </c>
       <c r="C59">
         <f>(B59/B71-1)*100</f>
@@ -1164,10 +1166,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>51900</v>
+        <v>53700</v>
       </c>
       <c r="C60">
         <f>(B60/B72-1)*100</f>
@@ -1176,10 +1178,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C61">
         <f>(B61/B73-1)*100</f>
@@ -1188,10 +1190,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>52400</v>
+        <v>51800</v>
       </c>
       <c r="C62">
         <f>(B62/B74-1)*100</f>
@@ -1200,10 +1202,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>56700</v>
+        <v>52400</v>
       </c>
       <c r="C63">
         <f>(B63/B75-1)*100</f>
@@ -1212,10 +1214,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="C64">
         <f>(B64/B76-1)*100</f>
@@ -1224,10 +1226,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>66300</v>
+        <v>60300</v>
       </c>
       <c r="C65">
         <f>(B65/B77-1)*100</f>
@@ -1236,10 +1238,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>62900</v>
+        <v>66300</v>
       </c>
       <c r="C66">
         <f>(B66/B78-1)*100</f>
@@ -1248,10 +1250,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>62500</v>
+        <v>62900</v>
       </c>
       <c r="C67">
         <f>(B67/B79-1)*100</f>
@@ -1259,7 +1261,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
+      <c r="A68" s="6" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>62500</v>
+      </c>
       <c r="C68">
         <f>(B68/B80-1)*100</f>
         <v/>
@@ -1344,6 +1351,13 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
+      <c r="C80">
+        <f>(B80/B92-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
